--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_28-04-2026.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_28-04-2026.xlsx
@@ -573,7 +573,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>£12.35</t>
+          <t>£14.22</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -588,7 +588,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>£23.87</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>£15.03</t>
+          <t>£17.27</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -675,7 +675,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>£15.01</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Read timed out. (read timeout=30)</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -717,17 +717,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>£21.15</t>
+          <t>£21.50</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>£21.15</t>
+          <t>£21.50</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>£21.15</t>
+          <t>£21.50</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -757,7 +757,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>£18.26</t>
+          <t>£21.0</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -767,7 +767,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>£18.46</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Read timed out. (read timeout=30)</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -809,17 +809,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>£21.90</t>
+          <t>£22.00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>£21.90</t>
+          <t>£22.00</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>£21.90</t>
+          <t>£22.00</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>£19.51</t>
+          <t>£22.43</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -901,17 +901,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>£28.00</t>
+          <t>£28.25</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>£28.00</t>
+          <t>£28.25</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>£28.00</t>
+          <t>£28.25</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -941,7 +941,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>£24.3</t>
+          <t>£27.95</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>£27.38</t>
+          <t>£31.48</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>£29.0</t>
+          <t>£30.95</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1125,7 +1125,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>£26.51</t>
+          <t>£30.49</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1217,7 +1217,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>£30.14</t>
+          <t>£34.65</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1269,17 +1269,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>£37.75</t>
+          <t>£37.95</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>£37.75</t>
+          <t>£37.95</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>£37.75</t>
+          <t>£37.95</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1299,7 +1299,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>POA</t>
+          <t>£40.67</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>£33.35</t>
+          <t>£38.36</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1361,17 +1361,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>£36.95</t>
+          <t>£37.50</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>£36.95</t>
+          <t>£37.50</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>£36.95</t>
+          <t>£37.50</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1401,7 +1401,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>£33.35</t>
+          <t>£38.36</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>£39.07</t>
+          <t>£38.75</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1493,7 +1493,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>£40.34</t>
+          <t>£46.41</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1545,17 +1545,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>£47.32</t>
+          <t>£47.42</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>£47.32</t>
+          <t>£47.42</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>£47.32</t>
+          <t>£47.42</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1585,7 +1585,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>£41.72</t>
+          <t>£47.97</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1677,7 +1677,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>£47.28</t>
+          <t>£54.37</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>£51.05</t>
+          <t>£58.7</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1821,17 +1821,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>£56.28</t>
+          <t>£56.50</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>£56.28</t>
+          <t>£56.50</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>£56.28</t>
+          <t>£56.50</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>£50.08</t>
+          <t>£57.61</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1953,7 +1953,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>£802.86</t>
+          <t>£923.42</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -2045,7 +2045,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>£1079.81</t>
+          <t>£1241.8</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -2137,7 +2137,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>£46.75</t>
+          <t>£53.75</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -2229,7 +2229,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>£55.96</t>
+          <t>£64.36</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>£53.22</t>
+          <t>£53.18</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>£53.22</t>
+          <t>£53.18</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>£53.22</t>
+          <t>£53.18</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>£66.19</t>
+          <t>£76.11</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2373,17 +2373,17 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>£61.00</t>
+          <t>£57.15</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>£61.00</t>
+          <t>£57.15</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>£61.00</t>
+          <t>£57.15</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2413,7 +2413,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>£70.17</t>
+          <t>£80.68</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -2465,17 +2465,17 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>£62.85</t>
+          <t>£62.20</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>£62.85</t>
+          <t>£62.20</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>£62.85</t>
+          <t>£62.20</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2505,7 +2505,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>£52.16</t>
+          <t>£59.99</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2597,7 +2597,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>£49.79</t>
+          <t>£57.25</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2741,17 +2741,17 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>£62.50</t>
+          <t>£57.15</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>£62.50</t>
+          <t>£57.15</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>£62.50</t>
+          <t>£57.15</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -2781,7 +2781,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>£51.27</t>
+          <t>£58.97</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2873,7 +2873,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>£1338.1</t>
+          <t>£1539.1</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2925,17 +2925,17 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>£1,725.00</t>
+          <t>£1,745.00</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>£1,725.00</t>
+          <t>£1,745.00</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>£1,725.00</t>
+          <t>£1,745.00</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -2965,7 +2965,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>£1424.57</t>
+          <t>£1638.33</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -3057,7 +3057,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>£1387.2</t>
+          <t>£1595.2</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">

--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_28-04-2026.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_28-04-2026.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>POA</t>
+          <t>£23.87</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -598,7 +598,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>£14.0</t>
+          <t>£14.75</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -675,7 +675,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Read timed out. (read timeout=30)</t>
+          <t>£15.01</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Read timed out. (read timeout=30)</t>
+          <t>£18.46</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>£29.74</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -2587,7 +2587,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>£118.47</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
